--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/ILLINOIS_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/ILLINOIS_2022.xlsx
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C142">
@@ -3487,7 +3487,7 @@
         <v>470</v>
       </c>
       <c r="D174">
-        <v>0.009711546408794115</v>
+        <v>0.009711546408794116</v>
       </c>
     </row>
     <row r="175">
@@ -4657,7 +4657,7 @@
         <v>45</v>
       </c>
       <c r="D239">
-        <v>0.0009298289114802877</v>
+        <v>0.0009298289114802876</v>
       </c>
     </row>
     <row r="240">
@@ -5845,7 +5845,7 @@
         <v>45</v>
       </c>
       <c r="D305">
-        <v>0.0009298289114802877</v>
+        <v>0.0009298289114802876</v>
       </c>
     </row>
     <row r="306">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C338">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C348">
@@ -7249,7 +7249,7 @@
         <v>44</v>
       </c>
       <c r="D383">
-        <v>0.0009091660467807257</v>
+        <v>0.0009091660467807255</v>
       </c>
     </row>
     <row r="384">
@@ -7357,7 +7357,7 @@
         <v>44</v>
       </c>
       <c r="D389">
-        <v>0.0009091660467807257</v>
+        <v>0.0009091660467807255</v>
       </c>
     </row>
     <row r="390">
@@ -7663,7 +7663,7 @@
         <v>44</v>
       </c>
       <c r="D406">
-        <v>0.0009091660467807257</v>
+        <v>0.0009091660467807255</v>
       </c>
     </row>
     <row r="407">
@@ -8833,7 +8833,7 @@
         <v>45</v>
       </c>
       <c r="D471">
-        <v>0.0009298289114802877</v>
+        <v>0.0009298289114802876</v>
       </c>
     </row>
     <row r="472">
@@ -14017,7 +14017,7 @@
         <v>44</v>
       </c>
       <c r="D759">
-        <v>0.0009091660467807257</v>
+        <v>0.0009091660467807255</v>
       </c>
     </row>
     <row r="760">
@@ -14791,7 +14791,7 @@
         <v>45</v>
       </c>
       <c r="D802">
-        <v>0.0009298289114802877</v>
+        <v>0.0009298289114802876</v>
       </c>
     </row>
     <row r="803">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C812">
@@ -16177,7 +16177,7 @@
         <v>45</v>
       </c>
       <c r="D879">
-        <v>0.0009298289114802877</v>
+        <v>0.0009298289114802876</v>
       </c>
     </row>
     <row r="880">
@@ -17394,7 +17394,7 @@
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C947">
@@ -18312,7 +18312,7 @@
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C998">
@@ -18330,7 +18330,7 @@
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C999">
@@ -26592,7 +26592,7 @@
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1458">
@@ -26869,7 +26869,7 @@
         <v>44</v>
       </c>
       <c r="D1473">
-        <v>0.0009091660467807257</v>
+        <v>0.0009091660467807255</v>
       </c>
     </row>
     <row r="1474">
@@ -28003,7 +28003,7 @@
         <v>45</v>
       </c>
       <c r="D1536">
-        <v>0.0009298289114802877</v>
+        <v>0.0009298289114802876</v>
       </c>
     </row>
     <row r="1537">
@@ -28399,7 +28399,7 @@
         <v>47</v>
       </c>
       <c r="D1558">
-        <v>0.0009711546408794115</v>
+        <v>0.0009711546408794116</v>
       </c>
     </row>
     <row r="1559">
@@ -30505,7 +30505,7 @@
         <v>44</v>
       </c>
       <c r="D1675">
-        <v>0.0009091660467807257</v>
+        <v>0.0009091660467807255</v>
       </c>
     </row>
     <row r="1676">
